--- a/artfynd/A 60683-2022 artfynd.xlsx
+++ b/artfynd/A 60683-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60683-2022 artfynd.xlsx
+++ b/artfynd/A 60683-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16896146</v>
+        <v>95425094</v>
       </c>
       <c r="B2" t="n">
-        <v>86196</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4405</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörtsjöbodarna, 560 m SSO om, Jmt</t>
+          <t>Mörtsjöbodarna, Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534586.5364043411</v>
+        <v>534745</v>
       </c>
       <c r="R2" t="n">
-        <v>7009171.29288326</v>
+        <v>7009088</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-10-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-10-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,40 +757,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>drygt 100-årig, grov kalkbarrskog med lågörtsmattor</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94282381</v>
+        <v>16896146</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,38 +784,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>4405</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mörtsjöbodarna, Jmt</t>
+          <t>Mörtsjöbodarna, 560 m SSO om, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534666.616124198</v>
+        <v>534587</v>
       </c>
       <c r="R3" t="n">
-        <v>7009076.504009857</v>
+        <v>7009171</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,62 +861,66 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>drygt 100-årig, grov kalkbarrskog med lågörtsmattor</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94282375</v>
+        <v>94282337</v>
       </c>
       <c r="B4" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>101248</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -966,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534666.616124198</v>
+        <v>534725</v>
       </c>
       <c r="R4" t="n">
-        <v>7009076.504009857</v>
+        <v>7009009</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -999,19 +961,9 @@
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,15 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95425094</v>
+        <v>94282375</v>
       </c>
       <c r="B5" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,35 +1002,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörtsjöbodarna, Ragunda, Jmt</t>
+          <t>Mörtsjöbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534744.2089272474</v>
+        <v>534666</v>
       </c>
       <c r="R5" t="n">
-        <v>7009087.264190944</v>
+        <v>7009076</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,22 +1060,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,6 +1074,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1152,51 +1093,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95424654</v>
+        <v>95424613</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>222002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mörtsjöbodarna, Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534614.5000483792</v>
+        <v>534575</v>
       </c>
       <c r="R6" t="n">
-        <v>7009175.653127332</v>
+        <v>7009228</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1226,19 +1163,9 @@
           <t>2021-08-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,6 +1189,405 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>95424769</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ragunda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>534532</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7009137</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-08-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-08-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>94282381</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mörtsjöbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>534666</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7009076</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-06-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-06-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>95424628</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mörtsjöbodarna, Ragunda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>534575</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7009228</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-08-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-08-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>95424700</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mörtsjöbodarna, Ragunda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>534558</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7009152</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-08-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-08-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
